--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF86E91F-EB02-412B-B936-2866CEC66BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B153E85-F30E-4DB1-8DE9-F57D8276DA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="68">
   <si>
     <t>Booking</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t xml:space="preserve">Qasim Khan </t>
+  </si>
+  <si>
+    <t>Over Load On Saleman</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1519,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="G2" s="105" t="s">
         <v>2</v>
@@ -1647,45 +1650,45 @@
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>9</v>
+        <v>12.25</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.22500000000000001</v>
+        <v>0.30625000000000002</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1</v>
+        <v>1.3611111111111112</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>1.7013888888888891</v>
       </c>
       <c r="O4" s="30">
         <f>H4</f>
         <v>9</v>
       </c>
       <c r="P4" s="31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
       <c r="R4" s="30">
         <f>K4</f>
-        <v>9</v>
+        <v>12.25</v>
       </c>
       <c r="S4" s="31">
-        <v>8</v>
+        <v>12.25</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1</v>
+        <v>1.3611111111111112</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
@@ -1716,59 +1719,59 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>12</v>
+        <v>5.55</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.185</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>0.79285714285714282</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.3214285714285714</v>
       </c>
       <c r="O5" s="30">
         <f t="shared" ref="O5:O12" si="6">H5</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P5" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
         <f t="shared" ref="R5:R12" si="7">K5</f>
-        <v>12</v>
+        <v>5.55</v>
       </c>
       <c r="S5" s="12">
-        <v>9</v>
+        <v>5.07</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>0.91351351351351362</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>0.72428571428571431</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.91351351351351362</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1795,59 +1798,59 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>14.3</v>
+        <v>13.35</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.57200000000000006</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>1.588888888888889</v>
+        <v>3.3374999999999999</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>3.177777777777778</v>
+        <v>6.6749999999999998</v>
       </c>
       <c r="O6" s="30">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P6" s="12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>0.77777777777777779</v>
+        <v>0.25</v>
       </c>
       <c r="R6" s="30">
         <f t="shared" si="7"/>
-        <v>14.3</v>
+        <v>13.35</v>
       </c>
       <c r="S6" s="12">
-        <v>11.2</v>
+        <v>3</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>0.78321678321678312</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>1.5999999999999999</v>
+        <v>3</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>1.0069930069930069</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1874,61 +1877,63 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>11.92</v>
+        <v>7.8</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.39733333333333332</v>
+        <v>0.26</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>0.91692307692307695</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.5282051282051281</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="O7" s="30">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P7" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0.76923076923076927</v>
+        <v>0</v>
       </c>
       <c r="R7" s="30">
         <f t="shared" si="7"/>
-        <v>11.92</v>
+        <v>7.8</v>
       </c>
       <c r="S7" s="12">
-        <v>12.87</v>
+        <v>0</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>1.0796979865771812</v>
-      </c>
-      <c r="U7" s="11">
+        <v>0</v>
+      </c>
+      <c r="U7" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.2869999999999999</v>
-      </c>
-      <c r="V7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1.4036073825503355</v>
-      </c>
-      <c r="W7" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1953,61 +1958,63 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>12.9</v>
+        <v>26.3</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.64500000000000002</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.29</v>
+        <v>3.7571428571428571</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>3.2250000000000001</v>
+        <v>9.3928571428571423</v>
       </c>
       <c r="O8" s="30">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P8" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" s="30">
         <f t="shared" si="7"/>
-        <v>12.9</v>
+        <v>26.3</v>
       </c>
       <c r="S8" s="12">
-        <v>12.87</v>
+        <v>0</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.99767441860465111</v>
-      </c>
-      <c r="U8" s="11">
+        <v>0</v>
+      </c>
+      <c r="U8" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.2869999999999999</v>
-      </c>
-      <c r="V8" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.99767441860465111</v>
-      </c>
-      <c r="W8" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="9" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2103,17 +2110,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>70</v>
+        <v>70.349999999999994</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2121,7 +2128,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>17.587499999999999</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2129,33 +2136,33 @@
       </c>
       <c r="O10" s="30">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P10" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.5714285714285714</v>
+        <v>0.75</v>
       </c>
       <c r="R10" s="30">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>70.349999999999994</v>
       </c>
       <c r="S10" s="12">
-        <v>42</v>
+        <v>30.75</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>0.43710021321961623</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1.05</v>
+        <v>0.5828002842928216</v>
       </c>
       <c r="W10" s="34"/>
     </row>
@@ -2542,11 +2549,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.14933333333333335</v>
+        <v>0.10133333333333333</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2554,15 +2561,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>130.12</v>
+        <v>135.6</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="8">K19/J19</f>
-        <v>0.33797402597402598</v>
+        <v>0.35220779220779219</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.3235714285714288</v>
+        <v>3.5684210526315789</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2570,31 +2577,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="9">P19/O19</f>
-        <v>0.8035714285714286</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>130.12</v>
+        <v>135.6</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>95.94</v>
+        <v>51.07</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="10">S19/R19</f>
-        <v>0.73731939747924991</v>
+        <v>0.37662241887905606</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.1320000000000001</v>
+        <v>2.5535000000000001</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3456,11 +3463,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="26">+H30+H25+H19</f>
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>0.16927083333333334</v>
+        <v>0.12239583333333333</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3468,15 +3475,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="27">+K30+K25+K19</f>
-        <v>139.12</v>
+        <v>144.6</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="11"/>
-        <v>0.3530964467005076</v>
+        <v>0.36700507614213196</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>2.1403076923076925</v>
+        <v>3.076595744680851</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3484,31 +3491,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="28">+P30+P25+P19</f>
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="13"/>
-        <v>0.83076923076923082</v>
+        <v>0.61702127659574468</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>139.12</v>
+        <v>144.6</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="29">+S30+S25+S19</f>
-        <v>104.94</v>
+        <v>60.07</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="14"/>
-        <v>0.75431282346175954</v>
+        <v>0.41542185338865839</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.9433333333333334</v>
+        <v>2.0713793103448275</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>

--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B153E85-F30E-4DB1-8DE9-F57D8276DA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6828160-B570-4977-AE6D-D41F168F8F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="69">
   <si>
     <t>Booking</t>
   </si>
@@ -223,13 +223,16 @@
     <t>Aqeel Malik (SD)</t>
   </si>
   <si>
-    <t>Vacant (SD)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Qasim Khan </t>
   </si>
   <si>
-    <t>Over Load On Saleman</t>
+    <t xml:space="preserve">With Pending Supply </t>
+  </si>
+  <si>
+    <t>Nabeel Traders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riwand </t>
   </si>
 </sst>
 </file>
@@ -888,7 +891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1145,6 +1148,12 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1472,10 +1481,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7265625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.453125" style="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" bestFit="1" customWidth="1"/>
@@ -1483,66 +1492,62 @@
     <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.26953125" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.453125" customWidth="1"/>
-    <col min="17" max="17" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7265625" customWidth="1"/>
-    <col min="20" max="20" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7265625" customWidth="1"/>
-    <col min="22" max="22" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="99" t="s">
+      <c r="G1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="102" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="104"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="104" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="106"/>
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46206</v>
-      </c>
-      <c r="G2" s="105" t="s">
+        <v>46207</v>
+      </c>
+      <c r="G2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="106"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="106" t="s">
+      <c r="H2" s="108"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="106"/>
-      <c r="L2" s="107"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="109"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="105" t="s">
+      <c r="O2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="106" t="s">
+      <c r="P2" s="108"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="106"/>
-      <c r="T2" s="107"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="109"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -1640,59 +1645,59 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>12.25</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.30625000000000002</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.3611111111111112</v>
+        <v>1.4666666666666668</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.7013888888888891</v>
+        <v>1.8333333333333337</v>
       </c>
       <c r="O4" s="30">
         <f>H4</f>
-        <v>9</v>
-      </c>
-      <c r="P4" s="31">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="P4" s="96">
+        <v>11</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="R4" s="30">
         <f>K4</f>
-        <v>12.25</v>
-      </c>
-      <c r="S4" s="31">
-        <v>12.25</v>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="S4" s="96">
+        <v>11.3</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1</v>
+        <v>0.64204545454545459</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.3611111111111112</v>
+        <v>1.0272727272727273</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.70041322314049592</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1719,59 +1724,59 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>5.55</v>
+        <v>10.75</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.185</v>
+        <v>0.35833333333333334</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>0.79285714285714282</v>
+        <v>3.5833333333333335</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.3214285714285714</v>
+        <v>5.9722222222222223</v>
       </c>
       <c r="O5" s="30">
         <f t="shared" ref="O5:O12" si="6">H5</f>
-        <v>7</v>
-      </c>
-      <c r="P5" s="12">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="P5" s="97">
+        <v>0</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" s="30">
         <f t="shared" ref="R5:R12" si="7">K5</f>
-        <v>5.55</v>
-      </c>
-      <c r="S5" s="12">
-        <v>5.07</v>
+        <v>10.75</v>
+      </c>
+      <c r="S5" s="97">
+        <v>0</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.91351351351351362</v>
-      </c>
-      <c r="U5" s="11">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>0.72428571428571431</v>
-      </c>
-      <c r="V5" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.91351351351351362</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1798,61 +1803,63 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>13.35</v>
+        <v>15.05</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.53400000000000003</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>3.3374999999999999</v>
+        <v>1.6722222222222223</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>6.6749999999999998</v>
+        <v>3.3444444444444446</v>
       </c>
       <c r="O6" s="30">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="P6" s="12">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="P6" s="97">
+        <v>9</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="R6" s="30">
         <f t="shared" si="7"/>
-        <v>13.35</v>
-      </c>
-      <c r="S6" s="12">
-        <v>3</v>
+        <v>15.05</v>
+      </c>
+      <c r="S6" s="97">
+        <v>15.05</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>0.2247191011235955</v>
+        <v>1</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1.6722222222222223</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>0.898876404494382</v>
-      </c>
-      <c r="W6" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1877,63 +1884,61 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>1.1142857142857143</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.857142857142857</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="O7" s="30">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="P7" s="12">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P7" s="97">
+        <v>4</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R7" s="30">
         <f t="shared" si="7"/>
-        <v>7.8</v>
-      </c>
-      <c r="S7" s="12">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="S7" s="97">
+        <v>5.2</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="11" t="e">
+        <v>1.3</v>
+      </c>
+      <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" s="14" t="e">
+        <v>1.3</v>
+      </c>
+      <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>67</v>
-      </c>
+        <v>1.9500000000000002</v>
+      </c>
+      <c r="W7" s="34"/>
     </row>
     <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1958,62 +1963,62 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>26.3</v>
+        <v>21.4</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>1.3149999999999999</v>
+        <v>1.0699999999999998</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>3.7571428571428571</v>
+        <v>2.1399999999999997</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>9.3928571428571423</v>
+        <v>5.3499999999999988</v>
       </c>
       <c r="O8" s="30">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="P8" s="12">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P8" s="97">
+        <v>14</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R8" s="30">
         <f t="shared" si="7"/>
-        <v>26.3</v>
-      </c>
-      <c r="S8" s="12">
-        <v>0</v>
+        <v>21.4</v>
+      </c>
+      <c r="S8" s="97">
+        <v>46.45</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="11" t="e">
+        <v>2.1705607476635516</v>
+      </c>
+      <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" s="14" t="e">
+        <v>3.3178571428571431</v>
+      </c>
+      <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.5504005340453941</v>
       </c>
       <c r="W8" s="34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -2063,7 +2068,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P9" s="12"/>
+      <c r="P9" s="97"/>
       <c r="Q9" s="13" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
@@ -2072,7 +2077,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S9" s="12"/>
+      <c r="S9" s="97"/>
       <c r="T9" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -2110,17 +2115,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>70.349999999999994</v>
+        <v>40</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>17.587499999999999</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2136,33 +2141,33 @@
       </c>
       <c r="O10" s="30">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="P10" s="12">
+        <v>3</v>
+      </c>
+      <c r="P10" s="97">
         <v>3</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R10" s="30">
         <f t="shared" si="7"/>
-        <v>70.349999999999994</v>
-      </c>
-      <c r="S10" s="12">
-        <v>30.75</v>
+        <v>40</v>
+      </c>
+      <c r="S10" s="97">
+        <v>40</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.43710021321961623</v>
+        <v>1</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>10.25</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>0.5828002842928216</v>
+        <v>1</v>
       </c>
       <c r="W10" s="34"/>
     </row>
@@ -2254,7 +2259,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="30">
         <v>50</v>
@@ -2538,22 +2543,22 @@
       <c r="C19" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="98"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="100"/>
       <c r="G19" s="40">
         <f>SUM(G4:G18)</f>
         <v>375</v>
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.10133333333333333</v>
+        <v>0.11466666666666667</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2561,15 +2566,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>135.6</v>
+        <v>108.80000000000001</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="8">K19/J19</f>
-        <v>0.35220779220779219</v>
+        <v>0.28259740259740262</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>3.5684210526315789</v>
+        <v>2.5302325581395353</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2577,31 +2582,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="9">P19/O19</f>
-        <v>0.52631578947368418</v>
+        <v>0.95348837209302328</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>135.6</v>
+        <v>108.80000000000001</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>51.07</v>
+        <v>118</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="10">S19/R19</f>
-        <v>0.37662241887905606</v>
+        <v>1.0845588235294117</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.5535000000000001</v>
+        <v>2.8780487804878048</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -2994,11 +2999,11 @@
       <c r="C25" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="98"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="100"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
         <v>5</v>
@@ -3375,11 +3380,11 @@
       <c r="C30" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="96" t="s">
+      <c r="D30" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="100"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
         <v>4</v>
@@ -3463,11 +3468,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="26">+H30+H25+H19</f>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>0.12239583333333333</v>
+        <v>0.13541666666666666</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3475,15 +3480,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="27">+K30+K25+K19</f>
-        <v>144.6</v>
+        <v>117.80000000000001</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="11"/>
-        <v>0.36700507614213196</v>
+        <v>0.29898477157360409</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>3.076595744680851</v>
+        <v>2.2653846153846158</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3491,31 +3496,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="28">+P30+P25+P19</f>
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="13"/>
-        <v>0.61702127659574468</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>144.6</v>
+        <v>117.80000000000001</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="29">+S30+S25+S19</f>
-        <v>60.07</v>
+        <v>127</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="14"/>
-        <v>0.41542185338865839</v>
+        <v>1.0780984719864175</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>2.0713793103448275</v>
+        <v>2.54</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3591,24 +3596,24 @@
         <v>25</v>
       </c>
       <c r="F2" s="94">
-        <v>46205</v>
-      </c>
-      <c r="G2" s="105" t="s">
+        <v>46207</v>
+      </c>
+      <c r="G2" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="102" t="s">
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="104"/>
-      <c r="O2" s="108" t="s">
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="109"/>
+      <c r="P2" s="111"/>
     </row>
     <row r="3" spans="1:17" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3686,35 +3691,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9</f>
-        <v>14</v>
+        <f>5+9+9+11</f>
+        <v>34</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>2.3333333333333334E-2</v>
+        <v>5.6666666666666664E-2</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9</f>
-        <v>17.5</v>
+        <f>8.5+9+12+11</f>
+        <v>40.5</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>3.1818181818181815E-2</v>
+        <v>7.3636363636363639E-2</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>532.5</v>
+        <v>509.5</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>21.3</v>
+        <v>20.38</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.25</v>
+        <v>1.1911764705882353</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3744,39 +3749,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8</f>
-        <v>12</v>
+        <f>4+8+7</f>
+        <v>19</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>3.1666666666666669E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9</f>
-        <v>15.6</v>
+        <f>6.6+9+5</f>
+        <v>20.6</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>2.8363636363636362E-2</v>
+        <v>3.7454545454545456E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>534.4</v>
+        <v>529.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>21.375999999999998</v>
+        <v>21.175999999999998</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.3</v>
+        <v>1.0842105263157895</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.418181818181818</v>
+        <v>1.1827751196172249</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3803,38 +3808,39 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <v>9</v>
+        <f>9+1+9</f>
+        <v>19</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>1.4999999999999999E-2</v>
+        <v>3.1666666666666669E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <f>11+0</f>
-        <v>11</v>
+        <f>11+0+3+15</f>
+        <v>29</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.02</v>
+        <v>5.2727272727272727E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>21.56</v>
+        <v>20.84</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.2222222222222223</v>
+        <v>1.5263157894736843</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.3333333333333335</v>
+        <v>1.665071770334928</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3861,39 +3867,39 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+13</f>
-        <v>18</v>
+        <f>5+13+0+4</f>
+        <v>22</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.03</v>
+        <v>3.6666666666666667E-2</v>
       </c>
       <c r="J7" s="11">
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <f>7.1+13</f>
-        <v>20.100000000000001</v>
+        <f>7.1+13+0+5</f>
+        <v>25.1</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>3.6545454545454548E-2</v>
+        <v>4.5636363636363642E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>529.9</v>
+        <v>524.9</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>21.195999999999998</v>
+        <v>20.995999999999999</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1166666666666667</v>
+        <v>1.1409090909090909</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.2181818181818183</v>
+        <v>1.2446280991735539</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3920,39 +3926,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10</f>
-        <v>20</v>
+        <f>10+10+0+14</f>
+        <v>34</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>3.3333333333333333E-2</v>
+        <v>5.6666666666666664E-2</v>
       </c>
       <c r="J8" s="11">
         <v>550</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13</f>
-        <v>27.1</v>
+        <f>14.1+13+0+46</f>
+        <v>73.099999999999994</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>4.9272727272727274E-2</v>
+        <v>0.13290909090909089</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>522.9</v>
+        <v>476.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>20.916</v>
+        <v>19.076000000000001</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.355</v>
+        <v>2.15</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.4781818181818183</v>
+        <v>2.3454545454545452</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4032,39 +4038,39 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7</f>
-        <v>11</v>
+        <f>4+7+3+3</f>
+        <v>17</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>5.5E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="J10" s="11">
         <v>5000</v>
       </c>
       <c r="K10" s="12">
-        <f>70+42</f>
-        <v>112</v>
+        <f>70+42+31+40</f>
+        <v>183</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>2.24E-2</v>
+        <v>3.6600000000000001E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4888</v>
+        <v>4817</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>195.52</v>
+        <v>192.68</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>10.181818181818182</v>
+        <v>10.764705882352942</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.40727272727272729</v>
+        <v>0.43058823529411761</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4149,34 +4155,38 @@
       <c r="G12" s="11">
         <v>600</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="12">
+        <v>28</v>
+      </c>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.6666666666666669E-2</v>
       </c>
       <c r="J12" s="11">
         <v>750</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>19</v>
+      </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.5333333333333333E-2</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="O12" s="72" t="e">
+        <v>29.24</v>
+      </c>
+      <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P12" s="14" t="e">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.54285714285714282</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4196,27 +4206,35 @@
       <c r="E13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="49" t="s">
-        <v>45</v>
-      </c>
+      <c r="F13" s="49"/>
       <c r="G13" s="11"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="11">
-        <v>100</v>
-      </c>
+      <c r="I13" s="70" t="e">
+        <f t="shared" ref="I13:I15" si="7">H13/G13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J13" s="11"/>
       <c r="K13" s="12"/>
-      <c r="L13" s="71"/>
+      <c r="L13" s="71" t="e">
+        <f t="shared" ref="L13:L16" si="8">K13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="M13" s="12">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N13" s="14">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="O13" s="72"/>
-      <c r="P13" s="14"/>
+        <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="72" t="e">
+        <f t="shared" ref="O13:O16" si="10">K13/H13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P13" s="14" t="e">
+        <f t="shared" ref="P13:P16" si="11">L13/I13</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q13" s="34"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
@@ -4240,22 +4258,32 @@
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="12"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="11">
-        <v>100</v>
-      </c>
+      <c r="I14" s="70" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J14" s="11"/>
       <c r="K14" s="12"/>
-      <c r="L14" s="71"/>
+      <c r="L14" s="71" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="M14" s="12">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="14">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="14"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="72" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P14" s="14" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q14" s="34"/>
     </row>
     <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
@@ -4275,24 +4303,36 @@
         <v>22</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="70"/>
+      <c r="I15" s="70" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="12"/>
-      <c r="L15" s="71"/>
+      <c r="L15" s="71" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="M15" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O15" s="72"/>
-      <c r="P15" s="14"/>
+      <c r="O15" s="72" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P15" s="14" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q15" s="34"/>
     </row>
     <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
@@ -4311,23 +4351,43 @@
       <c r="E16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="49"/>
+      <c r="F16" s="49" t="s">
+        <v>67</v>
+      </c>
       <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="71"/>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
+      <c r="I16" s="70" t="e">
+        <f t="shared" ref="I16" si="12">H16/G16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J16" s="11">
+        <v>1500</v>
+      </c>
+      <c r="K16" s="12">
+        <v>300</v>
+      </c>
+      <c r="L16" s="71">
+        <f t="shared" si="8"/>
+        <v>0.2</v>
+      </c>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="72"/>
-      <c r="P16" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="O16" s="72">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+      <c r="P16" s="14" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q16" s="34"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
@@ -4414,46 +4474,46 @@
       <c r="C19" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="98"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="100"/>
       <c r="G19" s="40">
-        <f>SUM(G4:G14)</f>
+        <f>SUM(G4:G18)</f>
         <v>5000</v>
       </c>
-      <c r="H19" s="41">
-        <f>SUM(H4:H12)</f>
-        <v>96</v>
+      <c r="H19" s="40">
+        <f>SUM(H4:H18)</f>
+        <v>186</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>1.9199999999999998E-2</v>
+        <v>3.7199999999999997E-2</v>
       </c>
       <c r="J19" s="80">
-        <f>SUM(J4:J14)</f>
-        <v>10000</v>
-      </c>
-      <c r="K19" s="81">
-        <f>SUM(K4:K12)</f>
-        <v>221.3</v>
+        <f>SUM(J4:J18)</f>
+        <v>11300</v>
+      </c>
+      <c r="K19" s="80">
+        <f>SUM(K4:K18)</f>
+        <v>708.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>2.213E-2</v>
+        <v>6.2681415929203538E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9778.7000000000007</v>
+        <v>10591.7</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>391.14800000000002</v>
+        <v>423.66800000000001</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.3052083333333333</v>
+        <v>3.8080645161290319</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4481,36 +4541,36 @@
         <v>33</v>
       </c>
       <c r="G20" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H20" s="8">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I20" s="85">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J20" s="7">
         <v>500</v>
       </c>
       <c r="K20" s="8">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="L20" s="87">
         <f t="shared" si="1"/>
-        <v>0.29799999999999999</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M20" s="8">
         <f t="shared" si="5"/>
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>14.04</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="O20" s="86">
-        <f t="shared" ref="O20:O24" si="7">K20/H20</f>
-        <v>149</v>
+        <f t="shared" ref="O20:O24" si="13">K20/H20</f>
+        <v>1.25</v>
       </c>
       <c r="P20" s="10">
         <v>1</v>
@@ -4536,37 +4596,37 @@
       <c r="F21" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="11">
-        <v>1</v>
+      <c r="G21" s="7">
+        <v>50</v>
       </c>
       <c r="H21" s="12">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I21" s="70">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="J21" s="11">
         <v>500</v>
       </c>
       <c r="K21" s="12">
-        <v>348</v>
+        <v>33</v>
       </c>
       <c r="L21" s="71">
         <f t="shared" si="1"/>
-        <v>0.69599999999999995</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="M21" s="12">
         <f t="shared" si="5"/>
-        <v>152</v>
+        <v>467</v>
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>6.08</v>
+        <v>18.68</v>
       </c>
       <c r="O21" s="72">
-        <f t="shared" si="7"/>
-        <v>348</v>
+        <f t="shared" si="13"/>
+        <v>1.2222222222222223</v>
       </c>
       <c r="P21" s="14">
         <v>1</v>
@@ -4592,37 +4652,37 @@
       <c r="F22" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="11">
-        <v>1</v>
+      <c r="G22" s="7">
+        <v>50</v>
       </c>
       <c r="H22" s="12">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I22" s="70">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="J22" s="11">
         <v>500</v>
       </c>
       <c r="K22" s="12">
-        <v>281</v>
+        <v>36</v>
       </c>
       <c r="L22" s="71">
         <f t="shared" si="1"/>
-        <v>0.56200000000000006</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="M22" s="12">
         <f t="shared" si="5"/>
-        <v>219</v>
+        <v>464</v>
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>8.76</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="O22" s="72">
-        <f t="shared" si="7"/>
-        <v>281</v>
+        <f t="shared" si="13"/>
+        <v>1.5</v>
       </c>
       <c r="P22" s="14">
         <v>1</v>
@@ -4648,37 +4708,37 @@
       <c r="F23" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="11">
-        <v>1</v>
+      <c r="G23" s="7">
+        <v>50</v>
       </c>
       <c r="H23" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I23" s="70">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J23" s="11">
         <v>500</v>
       </c>
       <c r="K23" s="12">
-        <v>263</v>
+        <v>27</v>
       </c>
       <c r="L23" s="71">
         <f t="shared" si="1"/>
-        <v>0.52600000000000002</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="5"/>
-        <v>237</v>
+        <v>473</v>
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>9.48</v>
+        <v>18.920000000000002</v>
       </c>
       <c r="O23" s="72">
-        <f t="shared" si="7"/>
-        <v>263</v>
+        <f t="shared" si="13"/>
+        <v>1.08</v>
       </c>
       <c r="P23" s="14">
         <v>1</v>
@@ -4704,37 +4764,37 @@
       <c r="F24" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="G24" s="36">
-        <v>1</v>
+      <c r="G24" s="7">
+        <v>50</v>
       </c>
       <c r="H24" s="37">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I24" s="73">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J24" s="74">
         <v>500</v>
       </c>
       <c r="K24" s="75">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="L24" s="76">
         <f t="shared" si="1"/>
-        <v>0.20599999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="M24" s="75">
         <f t="shared" si="5"/>
-        <v>397</v>
+        <v>484</v>
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>15.88</v>
+        <v>19.36</v>
       </c>
       <c r="O24" s="78">
-        <f t="shared" si="7"/>
-        <v>103</v>
+        <f t="shared" si="13"/>
+        <v>1.1428571428571428</v>
       </c>
       <c r="P24" s="39">
         <v>1</v>
@@ -4751,46 +4811,46 @@
       <c r="C25" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="98"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="100"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="H25" s="41">
-        <f t="shared" ref="H25:K25" si="8">SUM(H20:H24)</f>
-        <v>5</v>
+        <f t="shared" ref="H25:K25" si="14">SUM(H20:H24)</f>
+        <v>118</v>
       </c>
       <c r="I25" s="79">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="J25" s="80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="K25" s="81">
-        <f t="shared" si="8"/>
-        <v>1144</v>
+        <f t="shared" si="14"/>
+        <v>147</v>
       </c>
       <c r="L25" s="82">
         <f>K25/J25</f>
-        <v>0.45760000000000001</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="M25" s="81">
         <f t="shared" si="5"/>
-        <v>1356</v>
+        <v>2353</v>
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>54.24</v>
+        <v>94.12</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
-        <v>228.8</v>
+        <v>1.2457627118644068</v>
       </c>
       <c r="P25" s="43">
         <f>AVERAGE(P20:P24)</f>
@@ -4818,36 +4878,36 @@
         <v>51</v>
       </c>
       <c r="G26" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H26" s="8">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I26" s="85">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="J26" s="7">
         <v>650</v>
       </c>
       <c r="K26" s="8">
-        <v>248</v>
+        <v>34</v>
       </c>
       <c r="L26" s="87">
         <f t="shared" si="1"/>
-        <v>0.38153846153846155</v>
+        <v>5.2307692307692305E-2</v>
       </c>
       <c r="M26" s="8">
         <f t="shared" si="5"/>
-        <v>402</v>
+        <v>616</v>
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>16.079999999999998</v>
+        <v>24.64</v>
       </c>
       <c r="O26" s="86">
-        <f t="shared" ref="O26:O29" si="9">K26/H26</f>
-        <v>248</v>
+        <f t="shared" ref="O26:O29" si="15">K26/H26</f>
+        <v>1.4166666666666667</v>
       </c>
       <c r="P26" s="10">
         <v>1</v>
@@ -4874,36 +4934,36 @@
         <v>52</v>
       </c>
       <c r="G27" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H27" s="12">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I27" s="70">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="J27" s="11">
         <v>600</v>
       </c>
       <c r="K27" s="12">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="L27" s="71">
         <f t="shared" si="1"/>
-        <v>0.27500000000000002</v>
+        <v>5.6666666666666664E-2</v>
       </c>
       <c r="M27" s="12">
         <f t="shared" si="5"/>
-        <v>435</v>
+        <v>566</v>
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>17.399999999999999</v>
+        <v>22.64</v>
       </c>
       <c r="O27" s="72">
-        <f t="shared" si="9"/>
-        <v>165</v>
+        <f t="shared" si="15"/>
+        <v>1.7894736842105263</v>
       </c>
       <c r="P27" s="14">
         <v>1</v>
@@ -4930,36 +4990,36 @@
         <v>53</v>
       </c>
       <c r="G28" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H28" s="12">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I28" s="70">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="J28" s="11">
         <v>600</v>
       </c>
       <c r="K28" s="12">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="L28" s="71">
         <f t="shared" si="1"/>
-        <v>0.33</v>
+        <v>4.3333333333333335E-2</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="5"/>
-        <v>402</v>
+        <v>574</v>
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>16.079999999999998</v>
+        <v>22.96</v>
       </c>
       <c r="O28" s="72">
-        <f t="shared" si="9"/>
-        <v>198</v>
+        <f t="shared" si="15"/>
+        <v>1.1304347826086956</v>
       </c>
       <c r="P28" s="14">
         <v>1</v>
@@ -4986,36 +5046,36 @@
         <v>28</v>
       </c>
       <c r="G29" s="36">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H29" s="37">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I29" s="73">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="J29" s="74">
         <v>650</v>
       </c>
       <c r="K29" s="75">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="L29" s="76">
         <f t="shared" si="1"/>
-        <v>0.2630769230769231</v>
+        <v>5.8461538461538461E-2</v>
       </c>
       <c r="M29" s="75">
         <f t="shared" si="5"/>
-        <v>479</v>
+        <v>612</v>
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>19.16</v>
+        <v>24.48</v>
       </c>
       <c r="O29" s="78">
-        <f t="shared" si="9"/>
-        <v>171</v>
+        <f t="shared" si="15"/>
+        <v>2.2352941176470589</v>
       </c>
       <c r="P29" s="39">
         <v>1</v>
@@ -5032,46 +5092,46 @@
       <c r="C30" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="96" t="s">
+      <c r="D30" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="100"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="H30" s="41">
-        <f t="shared" ref="H30:K30" si="10">SUM(H26:H29)</f>
-        <v>4</v>
+        <f t="shared" ref="H30:K30" si="16">SUM(H26:H29)</f>
+        <v>83</v>
       </c>
       <c r="I30" s="79">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="J30" s="80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>2500</v>
       </c>
       <c r="K30" s="81">
-        <f t="shared" si="10"/>
-        <v>782</v>
+        <f t="shared" si="16"/>
+        <v>132</v>
       </c>
       <c r="L30" s="82">
         <f>K30/J30</f>
-        <v>0.31280000000000002</v>
+        <v>5.28E-2</v>
       </c>
       <c r="M30" s="81">
         <f t="shared" si="5"/>
-        <v>1718</v>
+        <v>2368</v>
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>68.72</v>
+        <v>94.72</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
-        <v>195.5</v>
+        <v>1.5903614457831325</v>
       </c>
       <c r="P30" s="43">
         <f>AVERAGE(P26:P29)</f>
@@ -5092,39 +5152,39 @@
       <c r="F31" s="57"/>
       <c r="G31" s="20">
         <f>+G30+G25+G19</f>
-        <v>5009</v>
+        <v>5450</v>
       </c>
       <c r="H31" s="21">
-        <f t="shared" ref="H31:K31" si="11">+H30+H25+H19</f>
-        <v>105</v>
+        <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
+        <v>387</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>2.0962267917748054E-2</v>
+        <v>7.1009174311926604E-2</v>
       </c>
       <c r="J31" s="89">
-        <f t="shared" si="11"/>
-        <v>15000</v>
+        <f t="shared" si="17"/>
+        <v>16300</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="11"/>
-        <v>2147.3000000000002</v>
+        <f t="shared" si="17"/>
+        <v>987.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.14315333333333335</v>
+        <v>6.0570552147239262E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12852.7</v>
+        <v>15312.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>514.10800000000006</v>
+        <v>612.50800000000004</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>20.450476190476191</v>
+        <v>2.5511627906976742</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6828160-B570-4977-AE6D-D41F168F8F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA7F556-5DCE-498B-874D-A6168452353B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="71">
   <si>
     <t>Booking</t>
   </si>
@@ -226,13 +226,19 @@
     <t xml:space="preserve">Qasim Khan </t>
   </si>
   <si>
-    <t xml:space="preserve">With Pending Supply </t>
-  </si>
-  <si>
     <t>Nabeel Traders</t>
   </si>
   <si>
     <t xml:space="preserve">Riwand </t>
+  </si>
+  <si>
+    <t>Maqbool</t>
+  </si>
+  <si>
+    <t>Ghulam Ahmad</t>
+  </si>
+  <si>
+    <t>Noman Younas</t>
   </si>
 </sst>
 </file>
@@ -1486,17 +1492,17 @@
     <col min="4" max="4" width="18.26953125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="23.7265625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.453125" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" style="24" customWidth="1"/>
+    <col min="8" max="8" width="7.7265625" customWidth="1"/>
     <col min="9" max="9" width="5.54296875" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" customWidth="1"/>
+    <col min="11" max="11" width="8.81640625" customWidth="1"/>
+    <col min="12" max="12" width="5.54296875" customWidth="1"/>
+    <col min="13" max="15" width="7.1796875" customWidth="1"/>
+    <col min="16" max="16" width="8.7265625" customWidth="1"/>
+    <col min="17" max="18" width="7.1796875" customWidth="1"/>
+    <col min="19" max="19" width="8.7265625" customWidth="1"/>
+    <col min="20" max="22" width="7.1796875" customWidth="1"/>
     <col min="23" max="23" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1524,7 +1530,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1645,59 +1651,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>17.600000000000001</v>
+        <v>8</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.44000000000000006</v>
+        <v>0.2</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.4666666666666668</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.8333333333333337</v>
+        <v>0.90909090909090917</v>
       </c>
       <c r="O4" s="30">
-        <f>H4</f>
         <v>12</v>
       </c>
       <c r="P4" s="96">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.91666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R4" s="30">
-        <f>K4</f>
-        <v>17.600000000000001</v>
+        <v>18</v>
       </c>
       <c r="S4" s="96">
-        <v>11.3</v>
+        <v>17</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.64204545454545459</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.0272727272727273</v>
+        <v>1.7</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>0.70041322314049592</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1724,59 +1728,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.35833333333333334</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>3.5833333333333335</v>
+        <v>1.5714285714285714</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>5.9722222222222223</v>
+        <v>2.6190476190476186</v>
       </c>
       <c r="O5" s="30">
-        <f t="shared" ref="O5:O12" si="6">H5</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="R5" s="30">
-        <f t="shared" ref="R5:R12" si="7">K5</f>
-        <v>10.75</v>
+        <v>7</v>
       </c>
       <c r="S5" s="97">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="e">
+        <v>0.81428571428571428</v>
+      </c>
+      <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" s="14" t="e">
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.95000000000000007</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1803,63 +1805,59 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>15.05</v>
+        <v>13</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.60199999999999998</v>
+        <v>0.52</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>1.6722222222222223</v>
+        <v>1.625</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>3.3444444444444446</v>
+        <v>3.25</v>
       </c>
       <c r="O6" s="30">
-        <f t="shared" si="6"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P6" s="97">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R6" s="30">
-        <f t="shared" si="7"/>
-        <v>15.05</v>
+        <v>6</v>
       </c>
       <c r="S6" s="97">
-        <v>15.05</v>
+        <v>5</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>1.6722222222222223</v>
+        <v>2.5</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="W6" s="34" t="s">
-        <v>66</v>
-      </c>
+        <v>2.5000000000000004</v>
+      </c>
+      <c r="W6" s="34"/>
     </row>
     <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1894,49 +1892,47 @@
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.13166666666666668</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.65833333333333333</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.1111111111111112</v>
+        <v>1.0972222222222223</v>
       </c>
       <c r="O7" s="30">
-        <f t="shared" si="6"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P7" s="97">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R7" s="30">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S7" s="97">
-        <v>5.2</v>
-      </c>
-      <c r="T7" s="13">
+        <v>0</v>
+      </c>
+      <c r="T7" s="13" t="e">
         <f t="shared" si="4"/>
-        <v>1.3</v>
-      </c>
-      <c r="U7" s="11">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.3</v>
-      </c>
-      <c r="V7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1.9500000000000002</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W7" s="34"/>
     </row>
@@ -1973,53 +1969,49 @@
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>21.4</v>
+        <v>10</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>1.0699999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>2.1399999999999997</v>
+        <v>1</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>5.3499999999999988</v>
+        <v>2.5</v>
       </c>
       <c r="O8" s="30">
-        <f t="shared" si="6"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" s="97">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="R8" s="30">
-        <f t="shared" si="7"/>
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="S8" s="97">
-        <v>46.45</v>
+        <v>22.5</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>2.1705607476635516</v>
+        <v>0.9</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>3.3178571428571431</v>
+        <v>3.75</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.5504005340453941</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>66</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="W8" s="34"/>
     </row>
     <row r="9" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2065,7 +2057,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O9" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="O5:O12" si="6">H9</f>
         <v>0</v>
       </c>
       <c r="P9" s="97"/>
@@ -2074,7 +2066,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R9" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="R5:R12" si="7">K9</f>
         <v>0</v>
       </c>
       <c r="S9" s="97"/>
@@ -2114,26 +2106,22 @@
       <c r="G10" s="30">
         <v>25</v>
       </c>
-      <c r="H10" s="12">
-        <v>3</v>
-      </c>
+      <c r="H10" s="12"/>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
-      <c r="K10" s="12">
-        <v>40</v>
-      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>13.333333333333334</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2141,33 +2129,33 @@
       </c>
       <c r="O10" s="30">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" s="97">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R10" s="30">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S10" s="97">
-        <v>40</v>
-      </c>
-      <c r="T10" s="13">
+        <v>0</v>
+      </c>
+      <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="U10" s="11">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>13.333333333333334</v>
-      </c>
-      <c r="V10" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W10" s="34"/>
     </row>
@@ -2193,29 +2181,32 @@
       <c r="G11" s="30">
         <v>50</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="12">
+        <v>14</v>
+      </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J11" s="30">
         <v>200</v>
       </c>
-      <c r="K11" s="12"/>
+      <c r="K11" s="12">
+        <v>18</v>
+      </c>
       <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="e">
+        <v>0.09</v>
+      </c>
+      <c r="M11" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="14" t="e">
+        <v>1.2857142857142858</v>
+      </c>
+      <c r="N11" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.3214285714285714</v>
       </c>
       <c r="O11" s="30">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P11" s="12"/>
@@ -2224,7 +2215,6 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R11" s="30">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S11" s="12"/>
@@ -2264,29 +2254,32 @@
       <c r="G12" s="30">
         <v>50</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="12">
+        <v>15</v>
+      </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J12" s="30">
         <v>20</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>10</v>
+      </c>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11" t="e">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="14" t="e">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N12" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="O12" s="30">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P12" s="12"/>
@@ -2295,7 +2288,6 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R12" s="30">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S12" s="12"/>
@@ -2554,11 +2546,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.11466666666666667</v>
+        <v>0.18933333333333333</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2566,15 +2558,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>108.80000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="8">K19/J19</f>
-        <v>0.28259740259740262</v>
+        <v>0.1920779220779221</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.5302325581395353</v>
+        <v>1.0415492957746479</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2582,31 +2574,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="9">P19/O19</f>
-        <v>0.95348837209302328</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>108.80000000000001</v>
+        <v>56</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>118</v>
+        <v>50.2</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="10">S19/R19</f>
-        <v>1.0845588235294117</v>
+        <v>0.89642857142857146</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.8780487804878048</v>
+        <v>2.0916666666666668</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -2631,58 +2623,58 @@
         <v>32</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G20" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H20" s="8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I20" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J20" s="7">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K20" s="8">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" ref="L20:L31" si="11">K20/J20</f>
-        <v>1</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="M20" s="7">
         <f t="shared" ref="M20:M24" si="12">K20/H20</f>
-        <v>1</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="N20" s="10">
         <v>1</v>
       </c>
       <c r="O20" s="7">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P20" s="8">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" ref="Q20:Q31" si="13">P20/O20</f>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="R20" s="7">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="S20" s="8">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="T20" s="9">
         <f t="shared" ref="T20:T31" si="14">S20/R20</f>
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U20" s="7">
         <f t="shared" ref="U20:U24" si="15">S20/P20</f>
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="V20" s="10">
         <v>1</v>
@@ -2706,58 +2698,58 @@
         <v>32</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="G21" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H21" s="12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I21" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J21" s="11">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K21" s="12">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L21" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="M21" s="11">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="N21" s="14">
         <v>1</v>
       </c>
       <c r="O21" s="11">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P21" s="12">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="R21" s="11">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="S21" s="12">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="T21" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="U21" s="11">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="V21" s="14">
         <v>1</v>
@@ -2781,27 +2773,27 @@
         <v>32</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H22" s="12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J22" s="11">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K22" s="12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L22" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M22" s="11">
         <f t="shared" si="12"/>
@@ -2811,28 +2803,28 @@
         <v>1</v>
       </c>
       <c r="O22" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P22" s="12">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q22" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="R22" s="11">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="S22" s="12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T22" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="U22" s="11">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="V22" s="14">
         <v>1</v>
@@ -2856,58 +2848,58 @@
         <v>32</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="G23" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H23" s="12">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="J23" s="11">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K23" s="12">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="L23" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M23" s="11">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2.6086956521739131</v>
       </c>
       <c r="N23" s="14">
         <v>1</v>
       </c>
       <c r="O23" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P23" s="12">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="R23" s="11">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="S23" s="12">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="T23" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.90476190476190477</v>
       </c>
       <c r="U23" s="11">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="V23" s="14">
         <v>1</v>
@@ -2931,58 +2923,58 @@
         <v>32</v>
       </c>
       <c r="F24" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="36">
         <v>50</v>
       </c>
-      <c r="G24" s="36">
-        <v>1</v>
-      </c>
       <c r="H24" s="37">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I24" s="38">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J24" s="36">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K24" s="37">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="M24" s="36">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="N24" s="39">
         <v>1</v>
       </c>
       <c r="O24" s="36">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="P24" s="37">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="38">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="R24" s="36">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="S24" s="37">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="T24" s="38">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U24" s="36">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>1.0588235294117647</v>
       </c>
       <c r="V24" s="39">
         <v>1</v>
@@ -3006,31 +2998,31 @@
       <c r="F25" s="100"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="H25" s="41">
         <f t="shared" ref="H25" si="16">SUM(H20:H24)</f>
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="I25" s="42">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.372</v>
       </c>
       <c r="J25" s="40">
         <f>SUM(J20:J24)</f>
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="K25" s="41">
         <f t="shared" ref="K25" si="17">SUM(K20:K24)</f>
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="L25" s="42">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="M25" s="40">
         <f>K25/H25</f>
-        <v>1</v>
+        <v>1.3225806451612903</v>
       </c>
       <c r="N25" s="43">
         <f>AVERAGE(N20:N24)</f>
@@ -3038,31 +3030,31 @@
       </c>
       <c r="O25" s="40">
         <f>SUM(O20:O24)</f>
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="P25" s="41">
         <f t="shared" ref="P25" si="18">SUM(P20:P24)</f>
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="Q25" s="42">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.89534883720930236</v>
       </c>
       <c r="R25" s="40">
         <f>SUM(R20:R24)</f>
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="S25" s="41">
         <f t="shared" ref="S25" si="19">SUM(S20:S24)</f>
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="T25" s="42">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.8990825688073395</v>
       </c>
       <c r="U25" s="40">
         <f>S25/P25</f>
-        <v>1</v>
+        <v>1.2727272727272727</v>
       </c>
       <c r="V25" s="43">
         <f>AVERAGE(V20:V24)</f>
@@ -3090,55 +3082,55 @@
         <v>51</v>
       </c>
       <c r="G26" s="7">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="H26" s="8">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J26" s="7">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="K26" s="8">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="L26" s="9">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M26" s="7">
         <f t="shared" ref="M26:M29" si="20">K26/H26</f>
-        <v>1</v>
+        <v>2.35</v>
       </c>
       <c r="N26" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="7">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P26" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="9">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="7">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="S26" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="9">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="U26" s="7">
+        <v>0</v>
+      </c>
+      <c r="U26" s="7" t="e">
         <f t="shared" ref="U26:U29" si="21">S26/P26</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V26" s="10">
         <v>1</v>
@@ -3165,55 +3157,55 @@
         <v>52</v>
       </c>
       <c r="G27" s="11">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="H27" s="12">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J27" s="11">
-        <v>1</v>
+        <v>2.3333333333333334E-2</v>
+      </c>
+      <c r="J27" s="7">
+        <v>500</v>
       </c>
       <c r="K27" s="12">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L27" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="M27" s="11">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>2.1428571428571428</v>
       </c>
       <c r="N27" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="11">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P27" s="12">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q27" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="R27" s="11">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="S27" s="12">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="T27" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U27" s="11">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="V27" s="14">
         <v>1</v>
@@ -3240,51 +3232,51 @@
         <v>53</v>
       </c>
       <c r="G28" s="11">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="H28" s="12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J28" s="11">
-        <v>1</v>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="J28" s="7">
+        <v>500</v>
       </c>
       <c r="K28" s="12">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="L28" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="M28" s="11">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>1.85</v>
       </c>
       <c r="N28" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="11">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P28" s="12">
         <v>1</v>
       </c>
       <c r="Q28" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="R28" s="11">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="S28" s="12">
         <v>1</v>
       </c>
       <c r="T28" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2.7027027027027029E-2</v>
       </c>
       <c r="U28" s="11">
         <f t="shared" si="21"/>
@@ -3315,47 +3307,47 @@
         <v>28</v>
       </c>
       <c r="G29" s="36">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="H29" s="37">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I29" s="38">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J29" s="36">
-        <v>1</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J29" s="7">
+        <v>500</v>
       </c>
       <c r="K29" s="37">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="M29" s="36">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>1.7777777777777777</v>
       </c>
       <c r="N29" s="39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="36">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P29" s="37">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q29" s="38">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R29" s="36">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="S29" s="37">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T29" s="38">
         <f t="shared" si="14"/>
@@ -3363,7 +3355,7 @@
       </c>
       <c r="U29" s="36">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>1.7777777777777777</v>
       </c>
       <c r="V29" s="39">
         <v>1</v>
@@ -3387,63 +3379,63 @@
       <c r="F30" s="100"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
-        <v>4</v>
+        <v>2400</v>
       </c>
       <c r="H30" s="41">
         <f t="shared" ref="H30" si="22">SUM(H26:H29)</f>
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="I30" s="42">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2.6249999999999999E-2</v>
       </c>
       <c r="J30" s="40">
         <f>SUM(J26:J29)</f>
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="K30" s="41">
         <f t="shared" ref="K30" si="23">SUM(K26:K29)</f>
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="L30" s="42">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="M30" s="40">
         <f>K30/H30</f>
-        <v>1</v>
+        <v>2.0634920634920637</v>
       </c>
       <c r="N30" s="43">
         <f>AVERAGE(N26:N29)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="40">
         <f>SUM(O26:O29)</f>
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="P30" s="41">
         <f t="shared" ref="P30" si="24">SUM(P26:P29)</f>
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="Q30" s="42">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.34920634920634919</v>
       </c>
       <c r="R30" s="40">
         <f>SUM(R26:R29)</f>
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="S30" s="41">
         <f t="shared" ref="S30" si="25">SUM(S26:S29)</f>
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="T30" s="42">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.33846153846153848</v>
       </c>
       <c r="U30" s="40">
         <f>S30/P30</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V30" s="43">
         <f>AVERAGE(V26:V29)</f>
@@ -3464,31 +3456,31 @@
       <c r="F31" s="57"/>
       <c r="G31" s="20">
         <f>+G30+G25+G19</f>
-        <v>384</v>
+        <v>3025</v>
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="26">+H30+H25+H19</f>
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>0.13541666666666666</v>
+        <v>7.5041322314049586E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
-        <v>394</v>
+        <v>2585</v>
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="27">+K30+K25+K19</f>
-        <v>117.80000000000001</v>
+        <v>326.95</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="11"/>
-        <v>0.29898477157360409</v>
+        <v>0.1264796905222437</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>2.2653846153846158</v>
+        <v>1.4403083700440529</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3496,31 +3488,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="28">+P30+P25+P19</f>
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="13"/>
-        <v>0.96153846153846156</v>
+        <v>0.67582417582417587</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>117.80000000000001</v>
+        <v>295</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="29">+S30+S25+S19</f>
-        <v>127</v>
+        <v>192.2</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="14"/>
-        <v>1.0780984719864175</v>
+        <v>0.6515254237288135</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>2.54</v>
+        <v>1.5626016260162601</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -4303,7 +4295,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="12"/>
@@ -4352,7 +4344,7 @@
         <v>22</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="12">

--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA7F556-5DCE-498B-874D-A6168452353B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FDA919-EA66-455E-8EBB-8786DA710291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="74">
   <si>
     <t>Booking</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>Noman Younas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M Saleh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M Hassan </t>
+  </si>
+  <si>
+    <t>Hamid</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1539,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1661,47 +1670,47 @@
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.2</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>0.72727272727272729</v>
+        <v>1.1818181818181819</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>0.90909090909090917</v>
+        <v>1.4772727272727273</v>
       </c>
       <c r="O4" s="30">
         <v>12</v>
       </c>
       <c r="P4" s="96">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="R4" s="30">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="S4" s="96">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.94444444444444442</v>
+        <v>0.75</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.7</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1.1333333333333333</v>
+        <v>1</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1738,47 +1747,47 @@
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>2.6190476190476186</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="R5" s="30">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S5" s="97">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.81428571428571428</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>0.95000000000000007</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.95000000000000007</v>
+        <v>1.9743589743589745</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1804,58 +1813,54 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12">
-        <v>8</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12">
-        <v>13</v>
-      </c>
+      <c r="K6" s="12"/>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.52</v>
-      </c>
-      <c r="M6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.625</v>
-      </c>
-      <c r="N6" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>3.25</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O6" s="30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P6" s="97">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
+        <v>0.875</v>
       </c>
       <c r="R6" s="30">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S6" s="97">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>0.83333333333333337</v>
+        <v>0.8</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>2.5</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>2.5000000000000004</v>
+        <v>0.91428571428571437</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1892,43 +1897,43 @@
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.13166666666666668</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>0.65833333333333333</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.0972222222222223</v>
+        <v>1.9444444444444446</v>
       </c>
       <c r="O7" s="30">
         <v>0</v>
       </c>
       <c r="P7" s="97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="13" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R7" s="30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S7" s="97">
-        <v>0</v>
-      </c>
-      <c r="T7" s="13" t="e">
+        <v>1.35</v>
+      </c>
+      <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" s="11" t="e">
+        <v>0.27</v>
+      </c>
+      <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.45</v>
       </c>
       <c r="V7" s="14" t="e">
         <f t="shared" si="5"/>
@@ -1959,57 +1964,57 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>2.7272727272727271</v>
       </c>
       <c r="O8" s="30">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P8" s="97">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R8" s="30">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="S8" s="97">
-        <v>22.5</v>
+        <v>10</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2057,7 +2062,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O9" s="30">
-        <f t="shared" ref="O5:O12" si="6">H9</f>
+        <f t="shared" ref="O9:O10" si="6">H9</f>
         <v>0</v>
       </c>
       <c r="P9" s="97"/>
@@ -2065,10 +2070,7 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R9" s="30">
-        <f t="shared" ref="R5:R12" si="7">K9</f>
-        <v>0</v>
-      </c>
+      <c r="R9" s="30"/>
       <c r="S9" s="97"/>
       <c r="T9" s="13" t="e">
         <f t="shared" si="4"/>
@@ -2131,20 +2133,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P10" s="97">
-        <v>0</v>
-      </c>
+      <c r="P10" s="97"/>
       <c r="Q10" s="13" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R10" s="30">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="97">
-        <v>0</v>
-      </c>
+      <c r="R10" s="30"/>
+      <c r="S10" s="97"/>
       <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
@@ -2181,30 +2176,26 @@
       <c r="G11" s="30">
         <v>50</v>
       </c>
-      <c r="H11" s="12">
-        <v>14</v>
-      </c>
+      <c r="H11" s="12"/>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="J11" s="30">
         <v>200</v>
       </c>
-      <c r="K11" s="12">
-        <v>18</v>
-      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>0.09</v>
-      </c>
-      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.2857142857142858</v>
-      </c>
-      <c r="N11" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>0.3214285714285714</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O11" s="30">
         <v>0</v>
@@ -2214,9 +2205,7 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R11" s="30">
-        <v>0</v>
-      </c>
+      <c r="R11" s="30"/>
       <c r="S11" s="12"/>
       <c r="T11" s="13" t="e">
         <f t="shared" si="4"/>
@@ -2254,30 +2243,26 @@
       <c r="G12" s="30">
         <v>50</v>
       </c>
-      <c r="H12" s="12">
-        <v>15</v>
-      </c>
+      <c r="H12" s="12"/>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="30">
         <v>20</v>
       </c>
-      <c r="K12" s="12">
-        <v>10</v>
-      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="M12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N12" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.6666666666666667</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O12" s="30">
         <v>0</v>
@@ -2287,9 +2272,7 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R12" s="30">
-        <v>0</v>
-      </c>
+      <c r="R12" s="30"/>
       <c r="S12" s="12"/>
       <c r="T12" s="13" t="e">
         <f t="shared" si="4"/>
@@ -2546,11 +2529,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.18933333333333333</v>
+        <v>9.3333333333333338E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2558,15 +2541,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>73.95</v>
+        <v>39</v>
       </c>
       <c r="L19" s="42">
-        <f t="shared" ref="L19" si="8">K19/J19</f>
-        <v>0.1920779220779221</v>
+        <f t="shared" ref="L19" si="7">K19/J19</f>
+        <v>0.1012987012987013</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.0415492957746479</v>
+        <v>1.1142857142857143</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2574,15 +2557,15 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="42">
-        <f t="shared" ref="Q19" si="9">P19/O19</f>
-        <v>0.72727272727272729</v>
+        <f t="shared" ref="Q19" si="8">P19/O19</f>
+        <v>0.76190476190476186</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
@@ -2590,15 +2573,15 @@
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>50.2</v>
+        <v>40.35</v>
       </c>
       <c r="T19" s="42">
-        <f t="shared" ref="T19" si="10">S19/R19</f>
-        <v>0.89642857142857146</v>
+        <f t="shared" ref="T19" si="9">S19/R19</f>
+        <v>0.72053571428571428</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.0916666666666668</v>
+        <v>1.2609375</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -2642,11 +2625,11 @@
         <v>17</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" ref="L20:L31" si="11">K20/J20</f>
+        <f t="shared" ref="L20:L31" si="10">K20/J20</f>
         <v>0.42499999999999999</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" ref="M20:M24" si="12">K20/H20</f>
+        <f t="shared" ref="M20:M24" si="11">K20/H20</f>
         <v>1.1333333333333333</v>
       </c>
       <c r="N20" s="10">
@@ -2659,7 +2642,7 @@
         <v>16</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:Q31" si="13">P20/O20</f>
+        <f t="shared" ref="Q20:Q31" si="12">P20/O20</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="R20" s="7">
@@ -2669,11 +2652,11 @@
         <v>22</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20:T31" si="14">S20/R20</f>
+        <f t="shared" ref="T20:T31" si="13">S20/R20</f>
         <v>0.88</v>
       </c>
       <c r="U20" s="7">
-        <f t="shared" ref="U20:U24" si="15">S20/P20</f>
+        <f t="shared" ref="U20:U24" si="14">S20/P20</f>
         <v>1.375</v>
       </c>
       <c r="V20" s="10">
@@ -2717,11 +2700,11 @@
         <v>13</v>
       </c>
       <c r="L21" s="13">
+        <f t="shared" si="10"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M21" s="11">
         <f t="shared" si="11"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" si="12"/>
         <v>0.65</v>
       </c>
       <c r="N21" s="14">
@@ -2734,7 +2717,7 @@
         <v>14</v>
       </c>
       <c r="Q21" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.93333333333333335</v>
       </c>
       <c r="R21" s="11">
@@ -2744,11 +2727,11 @@
         <v>19</v>
       </c>
       <c r="T21" s="13">
+        <f t="shared" si="13"/>
+        <v>0.95</v>
+      </c>
+      <c r="U21" s="11">
         <f t="shared" si="14"/>
-        <v>0.95</v>
-      </c>
-      <c r="U21" s="11">
-        <f t="shared" si="15"/>
         <v>1.3571428571428572</v>
       </c>
       <c r="V21" s="14">
@@ -2792,11 +2775,11 @@
         <v>20</v>
       </c>
       <c r="L22" s="13">
+        <f t="shared" si="10"/>
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="11">
         <f t="shared" si="11"/>
-        <v>0.5</v>
-      </c>
-      <c r="M22" s="11">
-        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N22" s="14">
@@ -2809,7 +2792,7 @@
         <v>15</v>
       </c>
       <c r="Q22" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="R22" s="11">
@@ -2819,11 +2802,11 @@
         <v>20</v>
       </c>
       <c r="T22" s="13">
+        <f t="shared" si="13"/>
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="U22" s="11">
         <f t="shared" si="14"/>
-        <v>0.86956521739130432</v>
-      </c>
-      <c r="U22" s="11">
-        <f t="shared" si="15"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="V22" s="14">
@@ -2867,11 +2850,11 @@
         <v>60</v>
       </c>
       <c r="L23" s="13">
+        <f t="shared" si="10"/>
+        <v>1.5</v>
+      </c>
+      <c r="M23" s="11">
         <f t="shared" si="11"/>
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="11">
-        <f t="shared" si="12"/>
         <v>2.6086956521739131</v>
       </c>
       <c r="N23" s="14">
@@ -2884,7 +2867,7 @@
         <v>15</v>
       </c>
       <c r="Q23" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="R23" s="11">
@@ -2894,11 +2877,11 @@
         <v>19</v>
       </c>
       <c r="T23" s="13">
+        <f t="shared" si="13"/>
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="U23" s="11">
         <f t="shared" si="14"/>
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="U23" s="11">
-        <f t="shared" si="15"/>
         <v>1.2666666666666666</v>
       </c>
       <c r="V23" s="14">
@@ -2942,11 +2925,11 @@
         <v>13</v>
       </c>
       <c r="L24" s="38">
+        <f t="shared" si="10"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M24" s="36">
         <f t="shared" si="11"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="M24" s="36">
-        <f t="shared" si="12"/>
         <v>0.8666666666666667</v>
       </c>
       <c r="N24" s="39">
@@ -2959,7 +2942,7 @@
         <v>17</v>
       </c>
       <c r="Q24" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.89473684210526316</v>
       </c>
       <c r="R24" s="36">
@@ -2969,11 +2952,11 @@
         <v>18</v>
       </c>
       <c r="T24" s="38">
+        <f t="shared" si="13"/>
+        <v>0.9</v>
+      </c>
+      <c r="U24" s="36">
         <f t="shared" si="14"/>
-        <v>0.9</v>
-      </c>
-      <c r="U24" s="36">
-        <f t="shared" si="15"/>
         <v>1.0588235294117647</v>
       </c>
       <c r="V24" s="39">
@@ -3001,7 +2984,7 @@
         <v>250</v>
       </c>
       <c r="H25" s="41">
-        <f t="shared" ref="H25" si="16">SUM(H20:H24)</f>
+        <f t="shared" ref="H25" si="15">SUM(H20:H24)</f>
         <v>93</v>
       </c>
       <c r="I25" s="42">
@@ -3013,11 +2996,11 @@
         <v>200</v>
       </c>
       <c r="K25" s="41">
-        <f t="shared" ref="K25" si="17">SUM(K20:K24)</f>
+        <f t="shared" ref="K25" si="16">SUM(K20:K24)</f>
         <v>123</v>
       </c>
       <c r="L25" s="42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0.61499999999999999</v>
       </c>
       <c r="M25" s="40">
@@ -3033,11 +3016,11 @@
         <v>86</v>
       </c>
       <c r="P25" s="41">
-        <f t="shared" ref="P25" si="18">SUM(P20:P24)</f>
+        <f t="shared" ref="P25" si="17">SUM(P20:P24)</f>
         <v>77</v>
       </c>
       <c r="Q25" s="42">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.89534883720930236</v>
       </c>
       <c r="R25" s="40">
@@ -3045,11 +3028,11 @@
         <v>109</v>
       </c>
       <c r="S25" s="41">
-        <f t="shared" ref="S25" si="19">SUM(S20:S24)</f>
+        <f t="shared" ref="S25" si="18">SUM(S20:S24)</f>
         <v>98</v>
       </c>
       <c r="T25" s="42">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.8990825688073395</v>
       </c>
       <c r="U25" s="40">
@@ -3079,31 +3062,31 @@
         <v>38</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G26" s="7">
         <v>600</v>
       </c>
       <c r="H26" s="8">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="0"/>
-        <v>3.3333333333333333E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J26" s="7">
         <v>500</v>
       </c>
       <c r="K26" s="8">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="11"/>
-        <v>9.4E-2</v>
+        <f t="shared" si="10"/>
+        <v>0.03</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" ref="M26:M29" si="20">K26/H26</f>
-        <v>2.35</v>
+        <f t="shared" ref="M26:M29" si="19">K26/H26</f>
+        <v>1.6666666666666667</v>
       </c>
       <c r="N26" s="10">
         <v>0</v>
@@ -3115,21 +3098,21 @@
         <v>0</v>
       </c>
       <c r="Q26" s="9">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>47</v>
+      </c>
+      <c r="S26" s="8">
+        <v>0</v>
+      </c>
+      <c r="T26" s="9">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R26" s="7">
-        <v>47</v>
-      </c>
-      <c r="S26" s="8">
-        <v>0</v>
-      </c>
-      <c r="T26" s="9">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
       <c r="U26" s="7" t="e">
-        <f t="shared" ref="U26:U29" si="21">S26/P26</f>
+        <f t="shared" ref="U26:U29" si="20">S26/P26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V26" s="10">
@@ -3154,31 +3137,31 @@
         <v>38</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G27" s="11">
         <v>600</v>
       </c>
       <c r="H27" s="12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v>2.3333333333333334E-2</v>
+        <v>0.02</v>
       </c>
       <c r="J27" s="7">
         <v>500</v>
       </c>
       <c r="K27" s="12">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L27" s="13">
-        <f t="shared" si="11"/>
-        <v>0.06</v>
+        <f t="shared" si="10"/>
+        <v>1.6E-2</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="20"/>
-        <v>2.1428571428571428</v>
+        <f t="shared" si="19"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N27" s="14">
         <v>0</v>
@@ -3187,25 +3170,25 @@
         <v>14</v>
       </c>
       <c r="P27" s="12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q27" s="13">
-        <f t="shared" si="13"/>
-        <v>0.8571428571428571</v>
+        <f t="shared" si="12"/>
+        <v>0.5</v>
       </c>
       <c r="R27" s="11">
         <v>30</v>
       </c>
       <c r="S27" s="12">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="T27" s="13">
-        <f t="shared" si="14"/>
-        <v>0.9</v>
+        <f t="shared" si="13"/>
+        <v>0.23333333333333334</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" si="21"/>
-        <v>2.25</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="V27" s="14">
         <v>1</v>
@@ -3229,31 +3212,31 @@
         <v>38</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="11">
         <v>600</v>
       </c>
       <c r="H28" s="12">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v>3.3333333333333333E-2</v>
+        <v>2.1666666666666667E-2</v>
       </c>
       <c r="J28" s="7">
         <v>500</v>
       </c>
       <c r="K28" s="12">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="L28" s="13">
-        <f t="shared" si="11"/>
-        <v>7.3999999999999996E-2</v>
+        <f t="shared" si="10"/>
+        <v>0.02</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="20"/>
-        <v>1.85</v>
+        <f t="shared" si="19"/>
+        <v>0.76923076923076927</v>
       </c>
       <c r="N28" s="14">
         <v>0</v>
@@ -3262,25 +3245,25 @@
         <v>20</v>
       </c>
       <c r="P28" s="12">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Q28" s="13">
-        <f t="shared" si="13"/>
-        <v>0.05</v>
+        <f t="shared" si="12"/>
+        <v>0.95</v>
       </c>
       <c r="R28" s="11">
         <v>37</v>
       </c>
       <c r="S28" s="12">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T28" s="13">
-        <f t="shared" si="14"/>
-        <v>2.7027027027027029E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.35135135135135137</v>
       </c>
       <c r="U28" s="11">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>0.68421052631578949</v>
       </c>
       <c r="V28" s="14">
         <v>1</v>
@@ -3304,31 +3287,31 @@
         <v>38</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="G29" s="36">
         <v>600</v>
       </c>
       <c r="H29" s="37">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I29" s="38">
         <f t="shared" si="0"/>
-        <v>1.4999999999999999E-2</v>
+        <v>1.8333333333333333E-2</v>
       </c>
       <c r="J29" s="7">
         <v>500</v>
       </c>
       <c r="K29" s="37">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L29" s="38">
-        <f t="shared" si="11"/>
-        <v>3.2000000000000001E-2</v>
+        <f t="shared" si="10"/>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="M29" s="36">
-        <f t="shared" si="20"/>
-        <v>1.7777777777777777</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="N29" s="39">
         <v>0</v>
@@ -3337,25 +3320,25 @@
         <v>9</v>
       </c>
       <c r="P29" s="37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="38">
-        <f t="shared" si="13"/>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>1.1111111111111112</v>
       </c>
       <c r="R29" s="36">
         <v>16</v>
       </c>
       <c r="S29" s="37">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T29" s="38">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="13"/>
+        <v>0.75</v>
       </c>
       <c r="U29" s="36">
-        <f t="shared" si="21"/>
-        <v>1.7777777777777777</v>
+        <f t="shared" si="20"/>
+        <v>1.2</v>
       </c>
       <c r="V29" s="39">
         <v>1</v>
@@ -3382,28 +3365,28 @@
         <v>2400</v>
       </c>
       <c r="H30" s="41">
-        <f t="shared" ref="H30" si="22">SUM(H26:H29)</f>
-        <v>63</v>
+        <f t="shared" ref="H30" si="21">SUM(H26:H29)</f>
+        <v>45</v>
       </c>
       <c r="I30" s="42">
         <f t="shared" si="0"/>
-        <v>2.6249999999999999E-2</v>
+        <v>1.8749999999999999E-2</v>
       </c>
       <c r="J30" s="40">
         <f>SUM(J26:J29)</f>
         <v>2000</v>
       </c>
       <c r="K30" s="41">
-        <f t="shared" ref="K30" si="23">SUM(K26:K29)</f>
-        <v>130</v>
+        <f t="shared" ref="K30" si="22">SUM(K26:K29)</f>
+        <v>44</v>
       </c>
       <c r="L30" s="42">
-        <f t="shared" si="11"/>
-        <v>6.5000000000000002E-2</v>
+        <f t="shared" si="10"/>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="M30" s="40">
         <f>K30/H30</f>
-        <v>2.0634920634920637</v>
+        <v>0.97777777777777775</v>
       </c>
       <c r="N30" s="43">
         <f>AVERAGE(N26:N29)</f>
@@ -3414,28 +3397,28 @@
         <v>63</v>
       </c>
       <c r="P30" s="41">
-        <f t="shared" ref="P30" si="24">SUM(P26:P29)</f>
-        <v>22</v>
+        <f t="shared" ref="P30" si="23">SUM(P26:P29)</f>
+        <v>36</v>
       </c>
       <c r="Q30" s="42">
-        <f t="shared" si="13"/>
-        <v>0.34920634920634919</v>
+        <f t="shared" si="12"/>
+        <v>0.5714285714285714</v>
       </c>
       <c r="R30" s="40">
         <f>SUM(R26:R29)</f>
         <v>130</v>
       </c>
       <c r="S30" s="41">
-        <f t="shared" ref="S30" si="25">SUM(S26:S29)</f>
-        <v>44</v>
+        <f t="shared" ref="S30" si="24">SUM(S26:S29)</f>
+        <v>32</v>
       </c>
       <c r="T30" s="42">
-        <f t="shared" si="14"/>
-        <v>0.33846153846153848</v>
+        <f t="shared" si="13"/>
+        <v>0.24615384615384617</v>
       </c>
       <c r="U30" s="40">
         <f>S30/P30</f>
-        <v>2</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="V30" s="43">
         <f>AVERAGE(V26:V29)</f>
@@ -3459,28 +3442,28 @@
         <v>3025</v>
       </c>
       <c r="H31" s="21">
-        <f t="shared" ref="H31" si="26">+H30+H25+H19</f>
-        <v>227</v>
+        <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
+        <v>173</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>7.5041322314049586E-2</v>
+        <v>5.7190082644628097E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
         <v>2585</v>
       </c>
       <c r="K31" s="21">
-        <f t="shared" ref="K31" si="27">+K30+K25+K19</f>
-        <v>326.95</v>
+        <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
+        <v>206</v>
       </c>
       <c r="L31" s="22">
-        <f t="shared" si="11"/>
-        <v>0.1264796905222437</v>
+        <f t="shared" si="10"/>
+        <v>7.9690522243713729E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.4403083700440529</v>
+        <v>1.1907514450867052</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3488,31 +3471,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="P31" s="21">
-        <f t="shared" ref="P31" si="28">+P30+P25+P19</f>
-        <v>123</v>
+        <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
+        <v>145</v>
       </c>
       <c r="Q31" s="22">
-        <f t="shared" si="13"/>
-        <v>0.67582417582417587</v>
+        <f t="shared" si="12"/>
+        <v>0.75916230366492143</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
         <v>295</v>
       </c>
       <c r="S31" s="21">
-        <f t="shared" ref="S31" si="29">+S30+S25+S19</f>
-        <v>192.2</v>
+        <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
+        <v>170.35</v>
       </c>
       <c r="T31" s="22">
-        <f t="shared" si="14"/>
-        <v>0.6515254237288135</v>
+        <f t="shared" si="13"/>
+        <v>0.57745762711864401</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.5626016260162601</v>
+        <v>1.1748275862068964</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3588,7 +3571,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="94">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3660,7 +3643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="29" t="s">
         <v>20</v>
       </c>
@@ -3683,42 +3666,42 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11</f>
-        <v>34</v>
+        <f>5+9+9+11+10</f>
+        <v>44</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>5.6666666666666664E-2</v>
+        <v>7.3333333333333334E-2</v>
       </c>
       <c r="J4" s="30">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9+12+11</f>
-        <v>40.5</v>
+        <f>8.5+9+12+11+17</f>
+        <v>57.5</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>7.3636363636363639E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>509.5</v>
+        <v>517.5</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>20.38</v>
+        <v>20.7</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1911764705882353</v>
+        <v>1.3068181818181819</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
       </c>
       <c r="Q4" s="34"/>
     </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
         <v>20</v>
       </c>
@@ -3737,47 +3720,47 @@
       <c r="F5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="30">
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7</f>
-        <v>19</v>
+        <f>4+8+7+17+7</f>
+        <v>43</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>3.1666666666666669E-2</v>
+        <v>7.166666666666667E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5</f>
-        <v>20.6</v>
+        <f>6.6+9+5+6</f>
+        <v>26.6</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>3.7454545454545456E-2</v>
+        <v>4.8363636363636366E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>529.4</v>
+        <v>523.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>21.175999999999998</v>
+        <v>20.936</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.0842105263157895</v>
+        <v>0.61860465116279073</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.1827751196172249</v>
+        <v>0.67484143763213533</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
         <v>20</v>
       </c>
@@ -3796,47 +3779,47 @@
       <c r="F6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="30">
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>9+1+9</f>
-        <v>19</v>
+        <f>9+1+9+2</f>
+        <v>21</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>3.1666666666666669E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <f>11+0+3+15</f>
-        <v>29</v>
+        <f>11+0+3+15+5</f>
+        <v>34</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>5.2727272727272727E-2</v>
+        <v>6.1818181818181821E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>20.84</v>
+        <v>20.64</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.5263157894736843</v>
+        <v>1.6190476190476191</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.665071770334928</v>
+        <v>1.7662337662337662</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
         <v>20</v>
       </c>
@@ -3855,7 +3838,7 @@
       <c r="F7" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="30">
         <v>600</v>
       </c>
       <c r="H7" s="12">
@@ -3895,7 +3878,7 @@
       </c>
       <c r="Q7" s="34"/>
     </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
         <v>20</v>
       </c>
@@ -3914,43 +3897,43 @@
       <c r="F8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="30">
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14</f>
-        <v>34</v>
+        <f>10+10+0+14+6</f>
+        <v>40</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>5.6666666666666664E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="J8" s="11">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46</f>
-        <v>73.099999999999994</v>
+        <f>14.1+13+0+46+23</f>
+        <v>96.1</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.13290909090909089</v>
+        <v>0.16713043478260869</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>476.9</v>
+        <v>478.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>19.076000000000001</v>
+        <v>19.155999999999999</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>2.15</v>
+        <v>2.4024999999999999</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.3454545454545452</v>
+        <v>2.5069565217391303</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3973,7 +3956,7 @@
       <c r="F9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="30">
         <v>600</v>
       </c>
       <c r="H9" s="12"/>
@@ -4038,7 +4021,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="J10" s="11">
-        <v>5000</v>
+        <v>4620</v>
       </c>
       <c r="K10" s="12">
         <f>70+42+31+40</f>
@@ -4046,15 +4029,15 @@
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>3.6600000000000001E-2</v>
+        <v>3.961038961038961E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4817</v>
+        <v>4437</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>192.68</v>
+        <v>177.48</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
@@ -4062,7 +4045,7 @@
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.43058823529411761</v>
+        <v>0.46600458365164243</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4097,7 +4080,7 @@
         <v>0.02</v>
       </c>
       <c r="J11" s="11">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="K11" s="12">
         <f>18+0</f>
@@ -4105,15 +4088,15 @@
       </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>2.4E-2</v>
+        <v>2.7692307692307693E-2</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>732</v>
+        <v>632</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>29.28</v>
+        <v>25.28</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4121,7 +4104,7 @@
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>1.3846153846153846</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4155,22 +4138,22 @@
         <v>4.6666666666666669E-2</v>
       </c>
       <c r="J12" s="11">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="K12" s="12">
         <v>19</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>2.5333333333333333E-2</v>
+        <v>3.4545454545454546E-2</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>731</v>
+        <v>531</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>29.24</v>
+        <v>21.24</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4178,7 +4161,7 @@
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>0.54285714285714282</v>
+        <v>0.74025974025974028</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4477,35 +4460,35 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>3.7199999999999997E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
-        <v>11300</v>
+        <v>10670</v>
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>708.3</v>
+        <v>759.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>6.2681415929203538E-2</v>
+        <v>7.1162136832239917E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>10591.7</v>
+        <v>9910.7000000000007</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>423.66800000000001</v>
+        <v>396.42800000000005</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.8080645161290319</v>
+        <v>3.3302631578947368</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -5148,35 +5131,35 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>7.1009174311926604E-2</v>
+        <v>7.8715596330275223E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
-        <v>16300</v>
+        <v>15670</v>
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>987.3</v>
+        <v>1038.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>6.0570552147239262E-2</v>
+        <v>6.6260370134014035E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>15312.7</v>
+        <v>14631.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>612.50800000000004</v>
+        <v>585.26800000000003</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.5511627906976742</v>
+        <v>2.4202797202797202</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FDA919-EA66-455E-8EBB-8786DA710291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCC31CC-031A-4241-8F32-97620DB3790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3560,15 +3560,15 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>7.407407407407407E-2</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F2" s="94">
         <v>46209</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>20.7</v>
+        <v>25.875</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>20.936</v>
+        <v>26.169999999999998</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>20.64</v>
+        <v>25.8</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>20.995999999999999</v>
+        <v>26.244999999999997</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>19.155999999999999</v>
+        <v>23.945</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>177.48</v>
+        <v>221.85</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>25.28</v>
+        <v>31.6</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>21.24</v>
+        <v>26.55</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>396.42800000000005</v>
+        <v>495.53500000000003</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>18.600000000000001</v>
+        <v>23.25</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>18.68</v>
+        <v>23.35</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>18.559999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>18.920000000000002</v>
+        <v>23.65</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>19.36</v>
+        <v>24.2</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>94.12</v>
+        <v>117.65</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>24.64</v>
+        <v>30.8</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>22.64</v>
+        <v>28.3</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>22.96</v>
+        <v>28.7</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>24.48</v>
+        <v>30.6</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>94.72</v>
+        <v>118.4</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>585.26800000000003</v>
+        <v>731.58500000000004</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>

--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCC31CC-031A-4241-8F32-97620DB3790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3538AB-D0D3-4FBC-813B-C14AC44307E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="75">
   <si>
     <t>Booking</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Hamid</t>
+  </si>
+  <si>
+    <t>Has Been resigned</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1542,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1660,57 +1663,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>13</v>
+        <v>17.25</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.32500000000000001</v>
+        <v>0.43125000000000002</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.1818181818181819</v>
+        <v>1.9166666666666667</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.4772727272727273</v>
+        <v>2.3958333333333335</v>
       </c>
       <c r="O4" s="30">
         <v>12</v>
       </c>
       <c r="P4" s="96">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.75</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="R4" s="30">
         <v>8</v>
       </c>
       <c r="S4" s="96">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.75</v>
+        <v>1.4375</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>0.66666666666666663</v>
+        <v>1.0454545454545454</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.5681818181818183</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1747,47 +1750,47 @@
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0.25833333333333336</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.1071428571428572</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.6666666666666665</v>
+        <v>1.8452380952380953</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="R5" s="30">
         <v>13</v>
       </c>
       <c r="S5" s="97">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.84615384615384615</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>3.6666666666666665</v>
+        <v>2</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1.9743589743589745</v>
+        <v>1.0769230769230771</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1813,7 +1816,9 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1821,7 +1826,9 @@
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1838,31 +1845,33 @@
         <v>8</v>
       </c>
       <c r="P6" s="97">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="R6" s="30">
         <v>15</v>
       </c>
       <c r="S6" s="97">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="U6" s="11">
+        <v>0</v>
+      </c>
+      <c r="U6" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.7142857142857142</v>
-      </c>
-      <c r="V6" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.91428571428571437</v>
-      </c>
-      <c r="W6" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1887,35 +1896,35 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0.11333333333333333</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
+        <v>0.85</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.9444444444444446</v>
+        <v>1.4166666666666665</v>
       </c>
       <c r="O7" s="30">
         <v>0</v>
       </c>
       <c r="P7" s="97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="13" t="e">
         <f t="shared" si="3"/>
@@ -1925,15 +1934,15 @@
         <v>5</v>
       </c>
       <c r="S7" s="97">
-        <v>1.35</v>
+        <v>5.8</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0.27</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>0.45</v>
+        <v>1.45</v>
       </c>
       <c r="V7" s="14" t="e">
         <f t="shared" si="5"/>
@@ -1974,47 +1983,47 @@
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>12</v>
+        <v>21.3</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>1.0649999999999999</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.0909090909090908</v>
+        <v>1.9363636363636365</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>2.7272727272727271</v>
+        <v>4.8409090909090908</v>
       </c>
       <c r="O8" s="30">
         <v>15</v>
       </c>
       <c r="P8" s="97">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="R8" s="30">
         <v>15</v>
       </c>
       <c r="S8" s="97">
-        <v>10</v>
+        <v>12.35</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.66666666666666663</v>
+        <v>0.82333333333333336</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.1227272727272728</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.1227272727272728</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2529,11 +2538,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>9.3333333333333338E-2</v>
+        <v>8.2666666666666666E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2541,15 +2550,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>39</v>
+        <v>49.7</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.1012987012987013</v>
+        <v>0.12909090909090909</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.1142857142857143</v>
+        <v>1.6032258064516129</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2561,11 +2570,11 @@
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.76190476190476186</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
@@ -2573,15 +2582,15 @@
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>40.35</v>
+        <v>33.65</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>0.72053571428571428</v>
+        <v>0.60089285714285712</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1.2609375</v>
+        <v>1.2017857142857142</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3443,11 +3452,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.7190082644628097E-2</v>
+        <v>5.586776859504132E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3455,15 +3464,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>206</v>
+        <v>216.7</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="10"/>
-        <v>7.9690522243713729E-2</v>
+        <v>8.3829787234042552E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.1907514450867052</v>
+        <v>1.2822485207100591</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3475,11 +3484,11 @@
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="12"/>
-        <v>0.75916230366492143</v>
+        <v>0.73821989528795806</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
@@ -3487,15 +3496,15 @@
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>170.35</v>
+        <v>163.65</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="13"/>
-        <v>0.57745762711864401</v>
+        <v>0.55474576271186438</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.1748275862068964</v>
+        <v>1.1606382978723404</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3525,10 +3534,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" customWidth="1"/>
+    <col min="5" max="5" width="23.7265625" customWidth="1"/>
     <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.26953125" style="24" customWidth="1"/>
     <col min="8" max="8" width="10.54296875" customWidth="1"/>
@@ -3560,18 +3569,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.25925925925925924</v>
+        <v>0.29629629629629628</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="94">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3666,35 +3675,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10</f>
-        <v>44</v>
+        <f>5+9+9+11+10+9</f>
+        <v>53</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>7.3333333333333334E-2</v>
+        <v>8.8333333333333333E-2</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9+12+11+17</f>
-        <v>57.5</v>
+        <f>8.5+9+12+11+17+6</f>
+        <v>63.5</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.1</v>
+        <v>0.11043478260869566</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>517.5</v>
+        <v>511.5</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>25.875</v>
+        <v>26.921052631578949</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.3068181818181819</v>
+        <v>1.1981132075471699</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3724,39 +3733,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7</f>
-        <v>43</v>
+        <f>4+8+7+17+7+3</f>
+        <v>46</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>7.166666666666667E-2</v>
+        <v>7.6666666666666661E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5+6</f>
-        <v>26.6</v>
+        <f>6.6+9+5+6+11</f>
+        <v>37.6</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>4.8363636363636366E-2</v>
+        <v>6.8363636363636363E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>523.4</v>
+        <v>512.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>26.169999999999998</v>
+        <v>26.968421052631577</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.61860465116279073</v>
+        <v>0.81739130434782614</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.67484143763213533</v>
+        <v>0.89169960474308307</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3783,39 +3792,39 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>9+1+9+2</f>
-        <v>21</v>
+        <f>9+1+9+2+7</f>
+        <v>28</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>3.5000000000000003E-2</v>
+        <v>4.6666666666666669E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <f>11+0+3+15+5</f>
-        <v>34</v>
+        <f>11+0+3+15+5+12</f>
+        <v>46</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>6.1818181818181821E-2</v>
+        <v>8.3636363636363634E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>25.8</v>
+        <v>26.526315789473685</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.6190476190476191</v>
+        <v>1.6428571428571428</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.7662337662337662</v>
+        <v>1.7922077922077921</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3842,39 +3851,39 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+13+0+4</f>
-        <v>22</v>
+        <f>5+13+0+4+3</f>
+        <v>25</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>3.6666666666666667E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="J7" s="11">
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <f>7.1+13+0+5</f>
-        <v>25.1</v>
+        <f>7.1+13+0+5+1</f>
+        <v>26.1</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>4.5636363636363642E-2</v>
+        <v>4.7454545454545458E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>524.9</v>
+        <v>523.9</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>26.244999999999997</v>
+        <v>27.573684210526313</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1409090909090909</v>
+        <v>1.044</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.2446280991735539</v>
+        <v>1.1389090909090911</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3901,39 +3910,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6</f>
-        <v>40</v>
+        <f>10+10+0+14+6+10</f>
+        <v>50</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46+23</f>
-        <v>96.1</v>
+        <f>14.1+13+0+46+23+10</f>
+        <v>106.1</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.16713043478260869</v>
+        <v>0.18452173913043476</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>478.9</v>
+        <v>468.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>23.945</v>
+        <v>24.678947368421053</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>2.4024999999999999</v>
+        <v>2.1219999999999999</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.5069565217391303</v>
+        <v>2.2142608695652175</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3978,7 +3987,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>27.5</v>
+        <v>28.94736842105263</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4037,7 +4046,7 @@
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>221.85</v>
+        <v>233.52631578947367</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
@@ -4096,7 +4105,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>31.6</v>
+        <v>33.263157894736842</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4153,7 +4162,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>26.55</v>
+        <v>27.94736842105263</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4353,7 +4362,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>63.157894736842103</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4460,11 +4469,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>4.5600000000000002E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4472,23 +4481,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>759.3</v>
+        <v>799.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>7.1162136832239917E-2</v>
+        <v>7.4910965323336451E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9910.7000000000007</v>
+        <v>9870.7000000000007</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>495.53500000000003</v>
+        <v>519.51052631578955</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.3302631578947368</v>
+        <v>3.0742307692307689</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4541,7 +4550,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>23.25</v>
+        <v>24.473684210526315</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4597,7 +4606,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>23.35</v>
+        <v>24.578947368421051</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4653,7 +4662,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>23.2</v>
+        <v>24.421052631578949</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4709,7 +4718,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>24.894736842105264</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4765,7 +4774,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>24.2</v>
+        <v>25.473684210526315</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4821,7 +4830,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>117.65</v>
+        <v>123.84210526315789</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4878,7 +4887,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>30.8</v>
+        <v>32.421052631578945</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4934,7 +4943,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>28.3</v>
+        <v>29.789473684210527</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4990,7 +4999,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>28.7</v>
+        <v>30.210526315789473</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5046,7 +5055,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>30.6</v>
+        <v>32.210526315789473</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5102,7 +5111,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>118.4</v>
+        <v>124.63157894736842</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5131,11 +5140,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>7.8715596330275223E-2</v>
+        <v>8.4587155963302754E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5143,23 +5152,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1038.3</v>
+        <v>1078.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>6.6260370134014035E-2</v>
+        <v>6.8813018506700699E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14631.7</v>
+        <v>14591.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>731.58500000000004</v>
+        <v>767.98421052631579</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.4202797202797202</v>
+        <v>2.3390455531453362</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3538AB-D0D3-4FBC-813B-C14AC44307E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA562335-AB18-4C36-9E92-B27079B839B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Has Been resigned</t>
+  </si>
+  <si>
+    <t>Saleman Issu</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1545,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1663,57 +1666,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>17.25</v>
+        <v>3</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.43125000000000002</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.9166666666666667</v>
+        <v>3</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>2.3958333333333335</v>
+        <v>3.75</v>
       </c>
       <c r="O4" s="30">
         <v>12</v>
       </c>
       <c r="P4" s="96">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.91666666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R4" s="30">
         <v>8</v>
       </c>
       <c r="S4" s="96">
-        <v>11.5</v>
+        <v>13.75</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1.4375</v>
+        <v>1.71875</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.0454545454545454</v>
+        <v>1.71875</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1.5681818181818183</v>
+        <v>2.578125</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1740,57 +1743,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>7.75</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.25833333333333336</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.1071428571428572</v>
+        <v>0.96666666666666656</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.8452380952380953</v>
+        <v>1.6111111111111112</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.2857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="R5" s="30">
         <v>13</v>
       </c>
       <c r="S5" s="97">
-        <v>4</v>
+        <v>6.37</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.30769230769230771</v>
+        <v>0.49</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1.274</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1.0769230769230771</v>
+        <v>0.68599999999999994</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1816,9 +1819,7 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12">
-        <v>0</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1826,9 +1827,7 @@
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12">
-        <v>0</v>
-      </c>
+      <c r="K6" s="12"/>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1844,22 +1843,18 @@
       <c r="O6" s="30">
         <v>8</v>
       </c>
-      <c r="P6" s="97">
-        <v>0</v>
-      </c>
+      <c r="P6" s="97"/>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R6" s="30">
-        <v>15</v>
-      </c>
-      <c r="S6" s="97">
         <v>0</v>
       </c>
-      <c r="T6" s="13">
+      <c r="S6" s="97"/>
+      <c r="T6" s="13" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="U6" s="11" t="e">
         <f t="shared" si="5"/>
@@ -1895,60 +1890,58 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12">
-        <v>4</v>
-      </c>
+      <c r="H7" s="12"/>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12">
-        <v>3.4</v>
-      </c>
+      <c r="K7" s="12"/>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.11333333333333333</v>
-      </c>
-      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>0.85</v>
-      </c>
-      <c r="N7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.4166666666666665</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="30">
+        <v>5</v>
+      </c>
+      <c r="P7" s="97">
         <v>0</v>
       </c>
-      <c r="P7" s="97">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="13" t="e">
+      <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R7" s="30">
         <v>5</v>
       </c>
       <c r="S7" s="97">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="U7" s="11">
+        <v>0</v>
+      </c>
+      <c r="U7" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.45</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V7" s="14" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W7" s="34"/>
+      <c r="W7" s="34" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1973,29 +1966,29 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>21.3</v>
+        <v>11.7</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>1.0649999999999999</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.9363636363636365</v>
+        <v>1.2999999999999998</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>4.8409090909090908</v>
+        <v>3.25</v>
       </c>
       <c r="O8" s="30">
         <v>15</v>
@@ -2011,19 +2004,19 @@
         <v>15</v>
       </c>
       <c r="S8" s="97">
-        <v>12.35</v>
+        <v>20.03</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.82333333333333336</v>
+        <v>1.3353333333333335</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1.1227272727272728</v>
+        <v>1.820909090909091</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.1227272727272728</v>
+        <v>1.8209090909090913</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2117,22 +2110,26 @@
       <c r="G10" s="30">
         <v>25</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="12">
+        <v>6</v>
+      </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="12">
+        <v>76</v>
+      </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="11" t="e">
+      <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>12.666666666666666</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2140,22 +2137,26 @@
       </c>
       <c r="O10" s="30">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="13" t="e">
+        <v>6</v>
+      </c>
+      <c r="P10" s="97">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.5</v>
       </c>
       <c r="R10" s="30"/>
-      <c r="S10" s="97"/>
+      <c r="S10" s="97">
+        <v>23</v>
+      </c>
       <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U10" s="11" t="e">
+      <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
@@ -2185,26 +2186,30 @@
       <c r="G11" s="30">
         <v>50</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="12">
+        <v>17</v>
+      </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="J11" s="30">
         <v>200</v>
       </c>
-      <c r="K11" s="12"/>
+      <c r="K11" s="12">
+        <v>28</v>
+      </c>
       <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="e">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M11" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="14" t="e">
+        <v>1.6470588235294117</v>
+      </c>
+      <c r="N11" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.41176470588235298</v>
       </c>
       <c r="O11" s="30">
         <v>0</v>
@@ -2252,26 +2257,30 @@
       <c r="G12" s="30">
         <v>50</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="12">
+        <v>3</v>
+      </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J12" s="30">
         <v>20</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>4</v>
+      </c>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11" t="e">
+        <v>0.2</v>
+      </c>
+      <c r="M12" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="14" t="e">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="N12" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="O12" s="30">
         <v>0</v>
@@ -2538,11 +2547,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>8.2666666666666666E-2</v>
+        <v>0.12</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2550,15 +2559,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>49.7</v>
+        <v>131.4</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.12909090909090909</v>
+        <v>0.34129870129870132</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.6032258064516129</v>
+        <v>2.92</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2566,31 +2575,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.66666666666666663</v>
+        <v>0.50943396226415094</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>33.65</v>
+        <v>63.150000000000006</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>0.60089285714285712</v>
+        <v>1.5402439024390244</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1.2017857142857142</v>
+        <v>2.338888888888889</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3452,11 +3461,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.586776859504132E-2</v>
+        <v>6.0495867768595044E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3464,15 +3473,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>216.7</v>
+        <v>298.39999999999998</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="10"/>
-        <v>8.3829787234042552E-2</v>
+        <v>0.11543520309477756</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.2822485207100591</v>
+        <v>1.6306010928961747</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3480,31 +3489,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="12"/>
-        <v>0.73821989528795806</v>
+        <v>0.69306930693069302</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>163.65</v>
+        <v>193.15</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="13"/>
-        <v>0.55474576271186438</v>
+        <v>0.68982142857142859</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.1606382978723404</v>
+        <v>1.3796428571428572</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3569,18 +3578,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.29629629629629628</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="94">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3675,35 +3684,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9</f>
-        <v>53</v>
+        <f>5+9+9+11+10+9+11</f>
+        <v>64</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>8.8333333333333333E-2</v>
+        <v>0.10666666666666667</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9+12+11+17+6</f>
-        <v>63.5</v>
+        <f>8.5+9+12+11+17+6+12</f>
+        <v>75.5</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.11043478260869566</v>
+        <v>0.13130434782608696</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>511.5</v>
+        <v>499.5</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>26.921052631578949</v>
+        <v>27.75</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1981132075471699</v>
+        <v>1.1796875</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3733,39 +3742,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3</f>
-        <v>46</v>
+        <f>4+8+7+17+7+3+2</f>
+        <v>48</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>7.6666666666666661E-2</v>
+        <v>0.08</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5+6+11</f>
-        <v>37.6</v>
+        <f>6.6+9+5+6+11+4</f>
+        <v>41.6</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>6.8363636363636363E-2</v>
+        <v>7.563636363636364E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>512.4</v>
+        <v>508.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>26.968421052631577</v>
+        <v>28.244444444444444</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.81739130434782614</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.89169960474308307</v>
+        <v>0.94545454545454544</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3816,7 +3825,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>26.526315789473685</v>
+        <v>28</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3851,39 +3860,39 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+13+0+4+3</f>
-        <v>25</v>
+        <f>5+13+0+4+3+4</f>
+        <v>29</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>4.1666666666666664E-2</v>
+        <v>4.8333333333333332E-2</v>
       </c>
       <c r="J7" s="11">
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <f>7.1+13+0+5+1</f>
-        <v>26.1</v>
+        <f>7.1+13+0+5+1+6</f>
+        <v>32.1</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>4.7454545454545458E-2</v>
+        <v>5.8363636363636368E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>523.9</v>
+        <v>517.9</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>27.573684210526313</v>
+        <v>28.772222222222222</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.044</v>
+        <v>1.106896551724138</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.1389090909090911</v>
+        <v>1.207523510971787</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3910,39 +3919,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10</f>
-        <v>50</v>
+        <f>10+10+0+14+6+10+11</f>
+        <v>61</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0.10166666666666667</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46+23+10</f>
-        <v>106.1</v>
+        <f>14.1+13+0+46+23+10+12</f>
+        <v>118.1</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.18452173913043476</v>
+        <v>0.20539130434782607</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>468.9</v>
+        <v>456.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>24.678947368421053</v>
+        <v>25.383333333333333</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>2.1219999999999999</v>
+        <v>1.9360655737704917</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.2142608695652175</v>
+        <v>2.0202423378474696</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3987,7 +3996,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>28.94736842105263</v>
+        <v>30.555555555555557</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4046,7 +4055,7 @@
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>233.52631578947367</v>
+        <v>246.5</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
@@ -4105,7 +4114,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>33.263157894736842</v>
+        <v>35.111111111111114</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4162,7 +4171,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>27.94736842105263</v>
+        <v>29.5</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4362,7 +4371,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>63.157894736842103</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4469,11 +4478,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>5.1999999999999998E-2</v>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4481,23 +4490,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>799.3</v>
+        <v>833.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>7.4910965323336451E-2</v>
+        <v>7.8097469540768502E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9870.7000000000007</v>
+        <v>9836.7000000000007</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>519.51052631578955</v>
+        <v>546.48333333333335</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.0742307692307689</v>
+        <v>2.8934027777777778</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4550,7 +4559,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>24.473684210526315</v>
+        <v>25.833333333333332</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4606,7 +4615,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>24.578947368421051</v>
+        <v>25.944444444444443</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4662,7 +4671,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>24.421052631578949</v>
+        <v>25.777777777777779</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4718,7 +4727,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>24.894736842105264</v>
+        <v>26.277777777777779</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4774,7 +4783,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>25.473684210526315</v>
+        <v>26.888888888888889</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4830,7 +4839,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>123.84210526315789</v>
+        <v>130.72222222222223</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4887,7 +4896,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>32.421052631578945</v>
+        <v>34.222222222222221</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4943,7 +4952,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>29.789473684210527</v>
+        <v>31.444444444444443</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4999,7 +5008,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>30.210526315789473</v>
+        <v>31.888888888888889</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5055,7 +5064,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>32.210526315789473</v>
+        <v>34</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5111,7 +5120,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>124.63157894736842</v>
+        <v>131.55555555555554</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5140,11 +5149,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>8.4587155963302754E-2</v>
+        <v>8.9724770642201829E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5152,23 +5161,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1078.3</v>
+        <v>1112.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>6.8813018506700699E-2</v>
+        <v>7.0982769623484362E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14591.7</v>
+        <v>14557.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>767.98421052631579</v>
+        <v>808.76111111111118</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.3390455531453362</v>
+        <v>2.2746421267893662</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>
